--- a/artfynd/A 37707-2025 artfynd.xlsx
+++ b/artfynd/A 37707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120553174</v>
+        <v>120553173</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520580</v>
+        <v>520374</v>
       </c>
       <c r="R2" t="n">
-        <v>6997925</v>
+        <v>6997890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gles, 140-årig tallskog på morän med fattigris och lav</t>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>3 substratenheter # mycket grova tallhögstubbar med brandspår</t>
+          <t>1 substratenheter # gammal tallstock</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,12 +792,7 @@
         <v>120553218</v>
       </c>
       <c r="B3" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120553171</v>
+        <v>120553215</v>
       </c>
       <c r="B4" t="n">
-        <v>78331</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,34 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ö om Sandtjärnen, Jmt</t>
+          <t>V om Fisksjöhögen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520480</v>
+        <v>520614</v>
       </c>
       <c r="R4" t="n">
-        <v>6997763</v>
+        <v>6997708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,9 +990,12 @@
           <t>140-årig tallskog på morän med fattigris och lav</t>
         </is>
       </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>gamla brandhögstubbar</t>
+          <t>1 substratenheter # bränd gammal tallåga i markplanet</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1022,6 +1010,573 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120553172</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ö om Sandtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520328</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6997814</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # typiska spår i grovbarkig, ca 280-årig tall</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120553171</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ö om Sandtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>520480</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6997763</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>gamla brandhögstubbar</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120553217</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>V om Fisksjöhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>520609</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6997695</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>3 substratenheter # grova brandhögstubbar</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120553174</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ö om Sandtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>520580</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6997925</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>gles, 140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>3 substratenheter # mycket grova tallhögstubbar med brandspår</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120553212</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>V om Fisksjöhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>520658</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6997883</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på morän med fattigris och lav</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov, 7 m hög skorstenshögstubbe med kolade ytor</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 37707-2025 artfynd.xlsx
+++ b/artfynd/A 37707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553173</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553215</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553172</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553217</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553174</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,8 +1621,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>